--- a/docs/data_source_log.xlsx
+++ b/docs/data_source_log.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="run_summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,64 +442,69 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>ticker_or_series</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sample_start</t>
+          <t>requested_start_date</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>sample_end</t>
+          <t>requested_end_date_exclusive</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>retrieved_at_utc</t>
+          <t>first_valid_date</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>actual_start</t>
+          <t>last_valid_date</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>actual_end</t>
+          <t>total_rows</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>n_observations</t>
+          <t>valid_observations</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>missing_observations</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>missing_rate_percent</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>download_time_utc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BTC_close</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,19 +514,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/quote/BTC-USD/history/</t>
+          <t>BTC-USD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>USD/BTC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>See source</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2018-01-01</t>
@@ -528,23 +534,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:19:34.121568+00:00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J2" t="n">
+        <v>2922</v>
       </c>
       <c r="K2" t="n">
         <v>2922</v>
@@ -552,16 +556,19 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:48:50.814114+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETH_close</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -571,19 +578,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/quote/ETH-USD/history/</t>
+          <t>ETH-USD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>USD/ETH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>See source</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
@@ -591,23 +598,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:19:34.121568+00:00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J3" t="n">
+        <v>2922</v>
       </c>
       <c r="K3" t="n">
         <v>2922</v>
@@ -615,9 +620,12 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:48:50.814114+00:00</t>
         </is>
       </c>
     </row>
@@ -634,17 +642,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/quote/^VIX/history/</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Index points</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>See source</t>
+          <t>Trading days</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -654,40 +662,41 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2018-01-02</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:19:34.121568+00:00</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2018-01-02</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J4" t="n">
+        <v>2922</v>
       </c>
       <c r="K4" t="n">
         <v>2011</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>OK</t>
+        <v>911</v>
+      </c>
+      <c r="M4" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:48:50.814114+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>USD_INDEX</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -697,17 +706,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/quote/DX-Y.NYB/history/</t>
+          <t>DX-Y.NYB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Index points</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>See source</t>
+          <t>Trading days</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -717,33 +726,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2018-01-02</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:19:34.121568+00:00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2018-01-02</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J5" t="n">
+        <v>2922</v>
       </c>
       <c r="K5" t="n">
         <v>2013</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>OK</t>
+        <v>909</v>
+      </c>
+      <c r="M5" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:48:50.814114+00:00</t>
         </is>
       </c>
     </row>
@@ -755,22 +765,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FRED - Federal Reserve Bank of St. Louis</t>
+          <t>Federal Reserve Bank of St. Louis (FRED)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=DGS2&amp;cosd=2018-01-01&amp;coed=2025-12-31</t>
+          <t>DGS2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Percent (%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>% per annum</t>
+          <t>Business days</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -780,33 +790,152 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2018-01-02</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:19:34.121568+00:00</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2018-01-02</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J6" t="n">
+        <v>2922</v>
       </c>
       <c r="K6" t="n">
-        <v>2087</v>
+        <v>1999</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>OK</t>
+        <v>923</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:48:50.814114+00:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Macro-crypto shock transmission</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>requested_start_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>requested_end_date_exclusive</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>raw_file</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>/Users/admin/Documents/macro-crypto-shock-transmission/data/raw/crypto_macro_raw.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>excel_file</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>/Users/admin/Documents/macro-crypto-shock-transmission/data/raw/crypto_macro_raw.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>number_of_rows</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>number_of_columns</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>download_time_utc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:48:50.814114+00:00</t>
         </is>
       </c>
     </row>
